--- a/tame_output/ON/bt/strategyON_20240701.xlsx
+++ b/tame_output/ON/bt/strategyON_20240701.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.1%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.7%</t>
+          <t>-523.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-163.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-211.2%</t>
+          <t>-209.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-170.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-73.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2010"/>
+  <dimension ref="A1:G2011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.711937966511798</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
@@ -47791,6 +47791,29 @@
       </c>
       <c r="G2010" t="n">
         <v>3.708463401406427</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B2011" t="n">
+        <v>3.754911907647114</v>
+      </c>
+      <c r="C2011" t="n">
+        <v>3.574210563329181</v>
+      </c>
+      <c r="D2011" t="n">
+        <v>-3.61778751548871</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>2.126739132819949</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>0.2455437415719411</v>
+      </c>
+      <c r="G2011" t="n">
+        <v>3.721536808272345</v>
       </c>
     </row>
   </sheetData>
